--- a/results/seed_runs/seed_results.xlsx
+++ b/results/seed_runs/seed_results.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>seed 101 artifact_mismatch: artifact early_stopped=true but manifest expects early stopping off; n_epochs=10 but manifest expects 2000; seed 102 missing_artifact: missing artifacts/probes/intphys2/seed_runs_v1/intphys2__jepa_v2__mlp__layer_40/seed_102/train_eval_summary.json</t>
+          <t>seed 101 missing_artifact: missing artifacts/probes/intphys2/seed_runs_v1/intphys2__jepa_v2__mlp__layer_40/seed_101/train_eval_summary.json; seed 102 missing_artifact: missing artifacts/probes/intphys2/seed_runs_v1/intphys2__jepa_v2__mlp__layer_40/seed_102/train_eval_summary.json</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       <c r="AB22"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD22">
@@ -5259,7 +5259,7 @@
       <c r="AB23"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD23">
@@ -5367,7 +5367,7 @@
       <c r="AB24"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD24">
@@ -5475,7 +5475,7 @@
       <c r="AB25"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD25">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD26">
@@ -5721,7 +5721,7 @@
       <c r="AB27"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD27">
@@ -5800,48 +5800,22 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>artifact_mismatch</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>voe_accuracy</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>voe_accuracy</t>
-        </is>
-      </c>
-      <c r="Q28">
-        <v>26.490066</v>
-      </c>
-      <c r="R28">
-        <v>51.15894</v>
-      </c>
-      <c r="S28">
-        <v>19.607843</v>
-      </c>
-      <c r="T28">
-        <v>51.960784</v>
-      </c>
-      <c r="U28">
-        <v>19.607843</v>
-      </c>
-      <c r="V28">
-        <v>51.960784</v>
-      </c>
-      <c r="W28">
-        <v>10</v>
-      </c>
+          <t>missing_artifact</t>
+        </is>
+      </c>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
       <c r="X28">
         <v>2000</v>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="Y28"/>
       <c r="Z28" t="inlineStr">
         <is>
           <t>false</t>
@@ -5852,14 +5826,10 @@
           <t>artifacts/probes/intphys2/seed_runs_v1/intphys2__jepa_v2__mlp__layer_40/seed_101/train_eval_summary.json</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>artifacts/probes/intphys2/seed_runs_v1/intphys2__jepa_v2__mlp__layer_40/seed_101/layer_40/eval</t>
-        </is>
-      </c>
+      <c r="AB28"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD28">
@@ -5870,7 +5840,7 @@
       <c r="AG28"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>artifact early_stopped=true but manifest expects early stopping off; n_epochs=10 but manifest expects 2000</t>
+          <t>missing artifacts/probes/intphys2/seed_runs_v1/intphys2__jepa_v2__mlp__layer_40/seed_101/train_eval_summary.json</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5937,7 @@
       <c r="AB29"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD29">
@@ -6075,7 +6045,7 @@
       <c r="AB30"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD30">
@@ -6183,7 +6153,7 @@
       <c r="AB31"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD31">
@@ -6291,7 +6261,7 @@
       <c r="AB32"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD32">
@@ -6399,7 +6369,7 @@
       <c r="AB33"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD33">
@@ -6507,7 +6477,7 @@
       <c r="AB34"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD34">
@@ -6615,7 +6585,7 @@
       <c r="AB35"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD35">
@@ -6723,7 +6693,7 @@
       <c r="AB36"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD36">
@@ -6831,7 +6801,7 @@
       <c r="AB37"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD37">
@@ -6939,7 +6909,7 @@
       <c r="AB38"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD38">
@@ -7047,7 +7017,7 @@
       <c r="AB39"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD39">
@@ -7155,7 +7125,7 @@
       <c r="AB40"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD40">
@@ -7263,7 +7233,7 @@
       <c r="AB41"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD41">
@@ -7371,7 +7341,7 @@
       <c r="AB42"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD42">
@@ -7479,7 +7449,7 @@
       <c r="AB43"/>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD43">
@@ -7587,7 +7557,7 @@
       <c r="AB44"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD44">
@@ -7695,7 +7665,7 @@
       <c r="AB45"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD45">
@@ -7803,7 +7773,7 @@
       <c r="AB46"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD46">
@@ -7911,7 +7881,7 @@
       <c r="AB47"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD47">
@@ -8019,7 +7989,7 @@
       <c r="AB48"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD48">
@@ -8127,7 +8097,7 @@
       <c r="AB49"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD49">
@@ -8235,7 +8205,7 @@
       <c r="AB50"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD50">
@@ -8343,7 +8313,7 @@
       <c r="AB51"/>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD51">
@@ -8451,7 +8421,7 @@
       <c r="AB52"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD52">
@@ -8559,7 +8529,7 @@
       <c r="AB53"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD53">
@@ -8667,7 +8637,7 @@
       <c r="AB54"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD54">
@@ -8775,7 +8745,7 @@
       <c r="AB55"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD55">
@@ -8883,7 +8853,7 @@
       <c r="AB56"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD56">
@@ -8991,7 +8961,7 @@
       <c r="AB57"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD57">
@@ -9099,7 +9069,7 @@
       <c r="AB58"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD58">
@@ -9207,7 +9177,7 @@
       <c r="AB59"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD59">
@@ -9315,7 +9285,7 @@
       <c r="AB60"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD60">
@@ -9423,7 +9393,7 @@
       <c r="AB61"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>results/seed_runs/seed_manifest_main_linear_mlp_v1.csv</t>
+          <t>results/verified_best_probe_configs.csv</t>
         </is>
       </c>
       <c r="AD61">
@@ -9470,7 +9440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09T07:56:16+00:00</t>
+          <t>2026-08-09T10:56:43+00:00</t>
         </is>
       </c>
     </row>
